--- a/output/pdf_financials_xlsx/FTEC.xlsx
+++ b/output/pdf_financials_xlsx/FTEC.xlsx
@@ -1845,13 +1845,13 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>2.009345</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>1.275016</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>2.601224</v>
       </c>
       <c r="E34" s="3" t="n">
         <v>0</v>
@@ -1931,13 +1931,13 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>2.009345</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>1.275016</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>2.601224</v>
       </c>
       <c r="E36" s="3" t="n">
         <v>0</v>
@@ -2447,13 +2447,13 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>2.139745</v>
+        <v>0.1304</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>1.381123</v>
+        <v>0.106107</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>13.146433</v>
+        <v>10.545209</v>
       </c>
       <c r="E48" s="3" t="n">
         <v>5.796454</v>
@@ -13786,7 +13786,7 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E100" s="5" t="n">

--- a/output/pdf_financials_xlsx/FTEC.xlsx
+++ b/output/pdf_financials_xlsx/FTEC.xlsx
@@ -3477,13 +3477,13 @@
         <v>0</v>
       </c>
       <c r="H70" s="3" t="n">
-        <v>0</v>
+        <v>0.11491</v>
       </c>
       <c r="I70" s="3" t="n">
-        <v>0</v>
+        <v>0.11491</v>
       </c>
       <c r="J70" s="3" t="n">
-        <v>0</v>
+        <v>0.06571399999999999</v>
       </c>
       <c r="K70" s="3" t="n">
         <v>0</v>
@@ -3520,13 +3520,13 @@
         <v>0</v>
       </c>
       <c r="H71" s="3" t="n">
-        <v>0</v>
+        <v>0.11491</v>
       </c>
       <c r="I71" s="3" t="n">
-        <v>0</v>
+        <v>0.11491</v>
       </c>
       <c r="J71" s="3" t="n">
-        <v>0</v>
+        <v>0.06571399999999999</v>
       </c>
       <c r="K71" s="3" t="n">
         <v>0</v>
@@ -3942,20 +3942,14 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H80" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I80" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J80" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H80" s="3" t="n">
+        <v>-0.04074344465241846</v>
+      </c>
+      <c r="I80" s="3" t="n">
+        <v>-0.04281850149777188</v>
+      </c>
+      <c r="J80" s="3" t="n">
+        <v>-0.04662286800805971</v>
       </c>
       <c r="K80" s="1" t="inlineStr">
         <is>
@@ -4787,7 +4781,7 @@
         <v>-1.58167</v>
       </c>
       <c r="C99" s="3" t="n">
-        <v>0.971365</v>
+        <v>-1.712636</v>
       </c>
       <c r="D99" s="3" t="n">
         <v>0.971365</v>
@@ -4796,25 +4790,25 @@
         <v>0.435089</v>
       </c>
       <c r="F99" s="3" t="n">
-        <v>-0.253513</v>
+        <v>0.765091</v>
       </c>
       <c r="G99" s="3" t="n">
         <v>-0.253513</v>
       </c>
       <c r="H99" s="3" t="n">
+        <v>0.405148</v>
+      </c>
+      <c r="I99" s="3" t="n">
         <v>-0.112797</v>
       </c>
-      <c r="I99" s="3" t="n">
+      <c r="J99" s="3" t="n">
         <v>1.196384</v>
-      </c>
-      <c r="J99" s="3" t="n">
-        <v>0.329212</v>
       </c>
       <c r="K99" s="3" t="n">
         <v>0.329212</v>
       </c>
       <c r="L99" s="3" t="n">
-        <v>-0.50075</v>
+        <v>0.489749</v>
       </c>
       <c r="M99" s="3" t="n">
         <v>-0.50075</v>
@@ -9542,7 +9536,11 @@
           <t>Current portion of lease obligations 9</t>
         </is>
       </c>
-      <c r="D43" t="inlineStr"/>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>CurrentCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E43" t="inlineStr">
         <is>
           <t>-</t>
@@ -9978,7 +9976,11 @@
           <t>Current portion of lease obligations 10</t>
         </is>
       </c>
-      <c r="D49" t="inlineStr"/>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>CurrentCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E49" t="inlineStr">
         <is>
           <t>-</t>
@@ -14764,7 +14766,11 @@
           <t>Net income (loss) $</t>
         </is>
       </c>
-      <c r="D113" t="inlineStr"/>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>NetIncomeFromContinuingOperations</t>
+        </is>
+      </c>
       <c r="E113" s="5" t="n">
         <v>-1.58167</v>
       </c>
@@ -20614,7 +20620,11 @@
           <t>Net income (loss) -- -- -- -- --</t>
         </is>
       </c>
-      <c r="D193" t="inlineStr"/>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>NetIncomeFromContinuingOperations</t>
+        </is>
+      </c>
       <c r="E193" t="inlineStr">
         <is>
           <t>-</t>
@@ -27026,7 +27036,11 @@
           <t>Net income (loss)</t>
         </is>
       </c>
-      <c r="D278" t="inlineStr"/>
+      <c r="D278" t="inlineStr">
+        <is>
+          <t>NetIncomeFromContinuingOperations</t>
+        </is>
+      </c>
       <c r="E278" s="5" t="n">
         <v>-2.586136</v>
       </c>
